--- a/panchang-data/Verona2026.xlsx
+++ b/panchang-data/Verona2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5411">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16258,6 +16258,9 @@
   </si>
   <si>
     <t>121°04'20.56</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16747,7 +16750,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16833,7 +16836,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16919,7 +16922,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -17005,7 +17008,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>90</v>
@@ -17091,7 +17094,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>109</v>
@@ -17177,7 +17180,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17263,7 +17266,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>142</v>
@@ -17349,7 +17352,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17435,7 +17438,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17521,7 +17524,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17607,7 +17610,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>90</v>
@@ -17693,7 +17696,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>109</v>
@@ -17779,7 +17782,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17865,7 +17868,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>142</v>
@@ -17951,7 +17954,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18037,7 +18040,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18123,7 +18126,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18209,7 +18212,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>90</v>
@@ -18295,7 +18298,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>109</v>
@@ -18381,7 +18384,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18467,7 +18470,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>142</v>
@@ -18553,7 +18556,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18639,7 +18642,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18725,7 +18728,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18811,7 +18814,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>90</v>
@@ -18897,7 +18900,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>109</v>
@@ -18983,7 +18986,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19069,7 +19072,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>142</v>
@@ -19155,7 +19158,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19241,7 +19244,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19327,7 +19330,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19413,7 +19416,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>571</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>90</v>
@@ -19499,7 +19502,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>109</v>
@@ -19585,7 +19588,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19671,7 +19674,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>142</v>
@@ -19757,7 +19760,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19843,7 +19846,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19929,7 +19932,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -20015,7 +20018,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>90</v>
@@ -20101,7 +20104,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>109</v>
@@ -20187,7 +20190,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20273,7 +20276,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>142</v>
@@ -20359,7 +20362,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20445,7 +20448,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20531,7 +20534,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20617,7 +20620,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>90</v>
@@ -20703,7 +20706,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>109</v>
@@ -20789,7 +20792,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20875,7 +20878,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>142</v>
@@ -20961,7 +20964,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21047,7 +21050,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21133,7 +21136,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21219,7 +21222,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>90</v>
@@ -21305,7 +21308,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>109</v>
@@ -21391,7 +21394,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21477,7 +21480,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>142</v>
@@ -21563,7 +21566,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21649,7 +21652,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21735,7 +21738,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21821,7 +21824,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>90</v>
@@ -21907,7 +21910,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>109</v>
@@ -21993,7 +21996,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>571</v>
+        <v>1014</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22079,7 +22082,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>142</v>
@@ -22165,7 +22168,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22251,7 +22254,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22337,7 +22340,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22423,7 +22426,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>90</v>
@@ -22509,7 +22512,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>109</v>
@@ -22595,7 +22598,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22681,7 +22684,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>142</v>
@@ -22767,7 +22770,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22853,7 +22856,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22939,7 +22942,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23025,7 +23028,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>90</v>
@@ -23111,7 +23114,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>109</v>
@@ -23197,7 +23200,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23283,7 +23286,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>142</v>
@@ -23369,7 +23372,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23455,7 +23458,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23541,7 +23544,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23627,7 +23630,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>90</v>
@@ -23713,7 +23716,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -23799,7 +23802,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23885,7 +23888,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>142</v>
@@ -23971,7 +23974,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24057,7 +24060,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24143,7 +24146,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24229,7 +24232,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>90</v>
@@ -24315,7 +24318,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>109</v>
@@ -24401,7 +24404,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24487,7 +24490,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1014</v>
+        <v>1438</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>142</v>
@@ -24573,7 +24576,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24659,7 +24662,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24745,7 +24748,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24831,7 +24834,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>90</v>
@@ -24917,7 +24920,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>109</v>
@@ -25003,7 +25006,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25089,7 +25092,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>142</v>
@@ -25175,7 +25178,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25261,7 +25264,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25347,7 +25350,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25433,7 +25436,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>90</v>
@@ -25519,7 +25522,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>109</v>
@@ -25605,7 +25608,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25691,7 +25694,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>142</v>
@@ -25777,7 +25780,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25863,7 +25866,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25949,7 +25952,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26035,7 +26038,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>90</v>
@@ -26121,7 +26124,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>109</v>
@@ -26207,7 +26210,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26293,7 +26296,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>142</v>
@@ -26379,7 +26382,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26465,7 +26468,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26551,7 +26554,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26637,7 +26640,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>90</v>
@@ -26723,7 +26726,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>109</v>
@@ -26809,7 +26812,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26895,7 +26898,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>142</v>
@@ -26981,7 +26984,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27067,7 +27070,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1438</v>
+        <v>1877</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27153,7 +27156,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27239,7 +27242,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>90</v>
@@ -27325,7 +27328,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>109</v>
@@ -27411,7 +27414,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27497,7 +27500,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>142</v>
@@ -27583,7 +27586,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27669,7 +27672,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27755,7 +27758,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27841,7 +27844,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>90</v>
@@ -27927,7 +27930,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>109</v>
@@ -28013,7 +28016,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28099,7 +28102,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>142</v>
@@ -28185,7 +28188,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28271,7 +28274,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28357,7 +28360,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1877</v>
+        <v>2315</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28443,7 +28446,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>90</v>
@@ -28529,7 +28532,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>109</v>
@@ -28615,7 +28618,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28701,7 +28704,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>142</v>
@@ -28787,7 +28790,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28873,7 +28876,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28959,7 +28962,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29045,7 +29048,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>90</v>
@@ -29131,7 +29134,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>109</v>
@@ -29217,7 +29220,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29303,7 +29306,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>142</v>
@@ -29389,7 +29392,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29475,7 +29478,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29561,7 +29564,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29647,7 +29650,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1877</v>
+        <v>5410</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>90</v>
@@ -29733,7 +29736,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>109</v>
@@ -29819,7 +29822,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29905,7 +29908,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>142</v>
@@ -29991,7 +29994,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30077,7 +30080,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30163,7 +30166,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30249,7 +30252,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>90</v>
@@ -30335,7 +30338,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>109</v>
@@ -30421,7 +30424,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30507,7 +30510,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>142</v>
@@ -30593,7 +30596,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30679,7 +30682,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30765,7 +30768,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30851,7 +30854,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2315</v>
+        <v>5410</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>90</v>
